--- a/artfynd/A 12578-2026 artfynd.xlsx
+++ b/artfynd/A 12578-2026 artfynd.xlsx
@@ -1005,7 +1005,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132499583</v>
+        <v>132498877</v>
       </c>
       <c r="B5" t="n">
         <v>57945</v>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>760164</v>
+        <v>760054</v>
       </c>
       <c r="R5" t="n">
-        <v>7177226</v>
+        <v>7177088</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>hack i gran</t>
+          <t>hack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1225,7 +1225,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132498877</v>
+        <v>132499583</v>
       </c>
       <c r="B7" t="n">
         <v>57945</v>
@@ -1268,10 +1268,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>760054</v>
+        <v>760164</v>
       </c>
       <c r="R7" t="n">
-        <v>7177088</v>
+        <v>7177226</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>hack på gran</t>
+          <t>hack i gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1441,10 +1441,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132498977</v>
+        <v>132497762</v>
       </c>
       <c r="B9" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1452,31 +1452,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1484,10 +1483,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>760051</v>
+        <v>759618</v>
       </c>
       <c r="R9" t="n">
-        <v>7177103</v>
+        <v>7177137</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1522,17 +1521,13 @@
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1661,10 +1656,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132497762</v>
+        <v>132499783</v>
       </c>
       <c r="B11" t="n">
-        <v>79317</v>
+        <v>91906</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1672,27 +1667,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1703,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>759618</v>
+        <v>759979</v>
       </c>
       <c r="R11" t="n">
-        <v>7177137</v>
+        <v>7177157</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1739,6 +1734,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>under en gammal, mossbelupen, grov granlåga</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1766,10 +1766,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132499783</v>
+        <v>132498977</v>
       </c>
       <c r="B12" t="n">
-        <v>91906</v>
+        <v>57948</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1777,30 +1777,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1808,10 +1809,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>759979</v>
+        <v>760051</v>
       </c>
       <c r="R12" t="n">
-        <v>7177157</v>
+        <v>7177103</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1848,16 +1849,15 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>under en gammal, mossbelupen, grov granlåga</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1876,10 +1876,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132499553</v>
+        <v>132497489</v>
       </c>
       <c r="B13" t="n">
-        <v>79317</v>
+        <v>57948</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,30 +1887,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1918,10 +1919,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>760162</v>
+        <v>759600</v>
       </c>
       <c r="R13" t="n">
-        <v>7177226</v>
+        <v>7177122</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1958,16 +1959,15 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>rikligt!</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1986,10 +1986,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132497489</v>
+        <v>132499553</v>
       </c>
       <c r="B14" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1997,31 +1997,30 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2029,10 +2028,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>759600</v>
+        <v>760162</v>
       </c>
       <c r="R14" t="n">
-        <v>7177122</v>
+        <v>7177226</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2069,15 +2068,16 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>rikligt!</t>
         </is>
       </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2531,10 +2531,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132498407</v>
+        <v>132498999</v>
       </c>
       <c r="B19" t="n">
-        <v>91892</v>
+        <v>57948</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2542,30 +2542,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2573,10 +2574,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>759734</v>
+        <v>760075</v>
       </c>
       <c r="R19" t="n">
-        <v>7177063</v>
+        <v>7177098</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2611,13 +2612,17 @@
           <t>2026-04-14</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2636,10 +2641,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132498999</v>
+        <v>132498407</v>
       </c>
       <c r="B20" t="n">
-        <v>57948</v>
+        <v>91892</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2647,31 +2652,30 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2679,10 +2683,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>760075</v>
+        <v>759734</v>
       </c>
       <c r="R20" t="n">
-        <v>7177098</v>
+        <v>7177063</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2717,17 +2721,13 @@
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2858,42 +2858,41 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132498370</v>
+        <v>132499759</v>
       </c>
       <c r="B22" t="n">
-        <v>57948</v>
+        <v>91855</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2901,10 +2900,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759732</v>
+        <v>759982</v>
       </c>
       <c r="R22" t="n">
-        <v>7177063</v>
+        <v>7177151</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2941,7 +2940,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>färska ringhack på grov tall</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2950,6 +2949,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2968,10 +2968,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132499759</v>
+        <v>132499049</v>
       </c>
       <c r="B23" t="n">
-        <v>91855</v>
+        <v>92316</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2979,21 +2979,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>4217</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3010,10 +3010,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>759982</v>
+        <v>760133</v>
       </c>
       <c r="R23" t="n">
-        <v>7177151</v>
+        <v>7177146</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3078,41 +3078,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132499049</v>
+        <v>132498370</v>
       </c>
       <c r="B24" t="n">
-        <v>92316</v>
+        <v>57948</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4217</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3120,10 +3121,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>760133</v>
+        <v>759732</v>
       </c>
       <c r="R24" t="n">
-        <v>7177146</v>
+        <v>7177063</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3160,7 +3161,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>färska ringhack på grov tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3169,7 +3170,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3403,10 +3403,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132497957</v>
+        <v>132499748</v>
       </c>
       <c r="B27" t="n">
-        <v>91892</v>
+        <v>89277</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3414,21 +3414,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>759681</v>
+        <v>760175</v>
       </c>
       <c r="R27" t="n">
-        <v>7177101</v>
+        <v>7177177</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3481,6 +3481,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>på toppbruten gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3508,10 +3513,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132499748</v>
+        <v>132497957</v>
       </c>
       <c r="B28" t="n">
-        <v>89277</v>
+        <v>91892</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3519,21 +3524,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3550,10 +3555,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>760175</v>
+        <v>759681</v>
       </c>
       <c r="R28" t="n">
-        <v>7177177</v>
+        <v>7177101</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3586,11 +3591,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>på toppbruten gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3724,7 +3724,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132499673</v>
+        <v>132498470</v>
       </c>
       <c r="B30" t="n">
         <v>57948</v>
@@ -3767,10 +3767,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>760160</v>
+        <v>759751</v>
       </c>
       <c r="R30" t="n">
-        <v>7177228</v>
+        <v>7177068</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3807,7 +3807,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>barksprätt på två granar</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3834,7 +3834,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132498470</v>
+        <v>132499673</v>
       </c>
       <c r="B31" t="n">
         <v>57948</v>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>759751</v>
+        <v>760160</v>
       </c>
       <c r="R31" t="n">
-        <v>7177068</v>
+        <v>7177228</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>barksprätt på två granar</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3944,10 +3944,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132499169</v>
+        <v>132497438</v>
       </c>
       <c r="B32" t="n">
-        <v>79317</v>
+        <v>57948</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3955,30 +3955,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3986,10 +3987,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>760150</v>
+        <v>759602</v>
       </c>
       <c r="R32" t="n">
-        <v>7177131</v>
+        <v>7177096</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4024,13 +4025,17 @@
           <t>2026-04-14</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>barksprätt på två granar</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF32" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4049,10 +4054,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132497438</v>
+        <v>132499169</v>
       </c>
       <c r="B33" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4060,31 +4065,30 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4092,10 +4096,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>759602</v>
+        <v>760150</v>
       </c>
       <c r="R33" t="n">
-        <v>7177096</v>
+        <v>7177131</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4130,17 +4134,13 @@
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>barksprätt på två granar</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4269,10 +4269,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132498603</v>
+        <v>132499026</v>
       </c>
       <c r="B35" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4280,31 +4280,30 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4312,10 +4311,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>759783</v>
+        <v>760140</v>
       </c>
       <c r="R35" t="n">
-        <v>7177071</v>
+        <v>7177159</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4350,17 +4349,13 @@
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4379,10 +4374,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132499026</v>
+        <v>132498603</v>
       </c>
       <c r="B36" t="n">
-        <v>79317</v>
+        <v>57948</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4390,30 +4385,31 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4421,10 +4417,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>760140</v>
+        <v>759783</v>
       </c>
       <c r="R36" t="n">
-        <v>7177159</v>
+        <v>7177071</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4459,13 +4455,17 @@
           <t>2026-04-14</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF36" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4484,42 +4484,42 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132498962</v>
+        <v>132497587</v>
       </c>
       <c r="B37" t="n">
-        <v>99098</v>
+        <v>57948</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4527,10 +4527,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>760052</v>
+        <v>759611</v>
       </c>
       <c r="R37" t="n">
-        <v>7177092</v>
+        <v>7177137</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4565,13 +4565,17 @@
           <t>2026-04-14</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF37" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4590,42 +4594,42 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132497587</v>
+        <v>132498962</v>
       </c>
       <c r="B38" t="n">
-        <v>57948</v>
+        <v>99098</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4633,10 +4637,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>759611</v>
+        <v>760052</v>
       </c>
       <c r="R38" t="n">
-        <v>7177137</v>
+        <v>7177092</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4671,17 +4675,13 @@
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4700,7 +4700,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132499504</v>
+        <v>132499538</v>
       </c>
       <c r="B39" t="n">
         <v>57945</v>
@@ -4743,10 +4743,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>760170</v>
+        <v>760162</v>
       </c>
       <c r="R39" t="n">
-        <v>7177214</v>
+        <v>7177226</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>hack i död gran</t>
+          <t>hack i död ved</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4915,7 +4915,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132498898</v>
+        <v>132499504</v>
       </c>
       <c r="B41" t="n">
         <v>57945</v>
@@ -4958,10 +4958,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>760051</v>
+        <v>760170</v>
       </c>
       <c r="R41" t="n">
-        <v>7177089</v>
+        <v>7177214</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5025,7 +5025,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132499538</v>
+        <v>132498898</v>
       </c>
       <c r="B42" t="n">
         <v>57945</v>
@@ -5068,10 +5068,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>760162</v>
+        <v>760051</v>
       </c>
       <c r="R42" t="n">
-        <v>7177226</v>
+        <v>7177089</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>hack i död ved</t>
+          <t>hack i död gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5135,7 +5135,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132499017</v>
+        <v>132499349</v>
       </c>
       <c r="B43" t="n">
         <v>79317</v>
@@ -5169,7 +5169,11 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5177,10 +5181,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>760089</v>
+        <v>760200</v>
       </c>
       <c r="R43" t="n">
-        <v>7177139</v>
+        <v>7177185</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5213,6 +5217,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>fertil!</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5350,7 +5359,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132499349</v>
+        <v>132499017</v>
       </c>
       <c r="B45" t="n">
         <v>79317</v>
@@ -5384,11 +5393,7 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5396,10 +5401,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>760200</v>
+        <v>760089</v>
       </c>
       <c r="R45" t="n">
-        <v>7177185</v>
+        <v>7177139</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5432,11 +5437,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>fertil!</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 12578-2026 artfynd.xlsx
+++ b/artfynd/A 12578-2026 artfynd.xlsx
@@ -2858,10 +2858,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132499759</v>
+        <v>132499049</v>
       </c>
       <c r="B22" t="n">
-        <v>91855</v>
+        <v>92316</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2869,21 +2869,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>4217</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759982</v>
+        <v>760133</v>
       </c>
       <c r="R22" t="n">
-        <v>7177151</v>
+        <v>7177146</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2968,41 +2968,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132499049</v>
+        <v>132498370</v>
       </c>
       <c r="B23" t="n">
-        <v>92316</v>
+        <v>57948</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4217</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3010,10 +3011,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>760133</v>
+        <v>759732</v>
       </c>
       <c r="R23" t="n">
-        <v>7177146</v>
+        <v>7177063</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3050,7 +3051,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>färska ringhack på grov tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3059,7 +3060,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3078,42 +3078,41 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132498370</v>
+        <v>132499759</v>
       </c>
       <c r="B24" t="n">
-        <v>57948</v>
+        <v>91855</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3121,10 +3120,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>759732</v>
+        <v>759982</v>
       </c>
       <c r="R24" t="n">
-        <v>7177063</v>
+        <v>7177151</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3161,7 +3160,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>färska ringhack på grov tall</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3170,6 +3169,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -4054,7 +4054,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132499169</v>
+        <v>132499026</v>
       </c>
       <c r="B33" t="n">
         <v>79317</v>
@@ -4096,10 +4096,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>760150</v>
+        <v>760140</v>
       </c>
       <c r="R33" t="n">
-        <v>7177131</v>
+        <v>7177159</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4159,10 +4159,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132499730</v>
+        <v>132498603</v>
       </c>
       <c r="B34" t="n">
-        <v>57945</v>
+        <v>57948</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4170,16 +4170,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4202,10 +4202,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>760153</v>
+        <v>759783</v>
       </c>
       <c r="R34" t="n">
-        <v>7177247</v>
+        <v>7177071</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4242,14 +4242,14 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>hack i rotben på gran</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG34" t="b">
         <v>0</v>
@@ -4269,7 +4269,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132499026</v>
+        <v>132499169</v>
       </c>
       <c r="B35" t="n">
         <v>79317</v>
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>760140</v>
+        <v>760150</v>
       </c>
       <c r="R35" t="n">
-        <v>7177159</v>
+        <v>7177131</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4374,10 +4374,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132498603</v>
+        <v>132499730</v>
       </c>
       <c r="B36" t="n">
-        <v>57948</v>
+        <v>57945</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4385,16 +4385,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4417,10 +4417,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>759783</v>
+        <v>760153</v>
       </c>
       <c r="R36" t="n">
-        <v>7177071</v>
+        <v>7177247</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4457,14 +4457,14 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>hack i rotben på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="b">
         <v>0</v>
@@ -4484,42 +4484,42 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132497587</v>
+        <v>132498962</v>
       </c>
       <c r="B37" t="n">
-        <v>57948</v>
+        <v>99098</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4527,10 +4527,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>759611</v>
+        <v>760052</v>
       </c>
       <c r="R37" t="n">
-        <v>7177137</v>
+        <v>7177092</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4565,17 +4565,13 @@
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4594,42 +4590,42 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132498962</v>
+        <v>132497587</v>
       </c>
       <c r="B38" t="n">
-        <v>99098</v>
+        <v>57948</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4637,10 +4633,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>760052</v>
+        <v>759611</v>
       </c>
       <c r="R38" t="n">
-        <v>7177092</v>
+        <v>7177137</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4675,13 +4671,17 @@
           <t>2026-04-14</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF38" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4810,10 +4810,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132499836</v>
+        <v>132499504</v>
       </c>
       <c r="B40" t="n">
-        <v>92191</v>
+        <v>57945</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4821,30 +4821,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4852,10 +4853,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>759978</v>
+        <v>760170</v>
       </c>
       <c r="R40" t="n">
-        <v>7177164</v>
+        <v>7177214</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4890,13 +4891,17 @@
           <t>2026-04-14</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>hack i död gran</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4915,10 +4920,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132499504</v>
+        <v>132499836</v>
       </c>
       <c r="B41" t="n">
-        <v>57945</v>
+        <v>92191</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4926,31 +4931,30 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4958,10 +4962,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>760170</v>
+        <v>759978</v>
       </c>
       <c r="R41" t="n">
-        <v>7177214</v>
+        <v>7177164</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4996,17 +5000,13 @@
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>hack i död gran</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12578-2026 artfynd.xlsx
+++ b/artfynd/A 12578-2026 artfynd.xlsx
@@ -1335,42 +1335,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132497859</v>
+        <v>132498977</v>
       </c>
       <c r="B8" t="n">
-        <v>99098</v>
+        <v>57948</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1378,10 +1378,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>759662</v>
+        <v>760051</v>
       </c>
       <c r="R8" t="n">
-        <v>7177107</v>
+        <v>7177103</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,13 +1416,17 @@
           <t>2026-04-14</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1441,41 +1445,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132497762</v>
+        <v>132497859</v>
       </c>
       <c r="B9" t="n">
-        <v>79317</v>
+        <v>99098</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1483,10 +1488,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>759618</v>
+        <v>759662</v>
       </c>
       <c r="R9" t="n">
-        <v>7177137</v>
+        <v>7177107</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,10 +1551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132497934</v>
+        <v>132497762</v>
       </c>
       <c r="B10" t="n">
-        <v>57945</v>
+        <v>79317</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,31 +1562,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1589,10 +1593,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>759675</v>
+        <v>759618</v>
       </c>
       <c r="R10" t="n">
-        <v>7177093</v>
+        <v>7177137</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1627,17 +1631,13 @@
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>bohål i ihålig asp</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1656,10 +1656,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132499783</v>
+        <v>132497934</v>
       </c>
       <c r="B11" t="n">
-        <v>91906</v>
+        <v>57945</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1667,30 +1667,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1204</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1698,10 +1699,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>759979</v>
+        <v>759675</v>
       </c>
       <c r="R11" t="n">
-        <v>7177157</v>
+        <v>7177093</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1738,7 +1739,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>under en gammal, mossbelupen, grov granlåga</t>
+          <t>bohål i ihålig asp</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1747,7 +1748,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1766,10 +1766,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132498977</v>
+        <v>132499783</v>
       </c>
       <c r="B12" t="n">
-        <v>57948</v>
+        <v>91906</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1777,31 +1777,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1809,10 +1808,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>760051</v>
+        <v>759979</v>
       </c>
       <c r="R12" t="n">
-        <v>7177103</v>
+        <v>7177157</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1849,15 +1848,16 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>under en gammal, mossbelupen, grov granlåga</t>
         </is>
       </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -4054,7 +4054,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132499026</v>
+        <v>132499169</v>
       </c>
       <c r="B33" t="n">
         <v>79317</v>
@@ -4096,10 +4096,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>760140</v>
+        <v>760150</v>
       </c>
       <c r="R33" t="n">
-        <v>7177159</v>
+        <v>7177131</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4159,10 +4159,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132498603</v>
+        <v>132499730</v>
       </c>
       <c r="B34" t="n">
-        <v>57948</v>
+        <v>57945</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4170,16 +4170,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4202,10 +4202,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>759783</v>
+        <v>760153</v>
       </c>
       <c r="R34" t="n">
-        <v>7177071</v>
+        <v>7177247</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4242,14 +4242,14 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>hack i rotben på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="b">
         <v>0</v>
@@ -4269,7 +4269,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132499169</v>
+        <v>132499026</v>
       </c>
       <c r="B35" t="n">
         <v>79317</v>
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>760150</v>
+        <v>760140</v>
       </c>
       <c r="R35" t="n">
-        <v>7177131</v>
+        <v>7177159</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4374,10 +4374,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132499730</v>
+        <v>132498603</v>
       </c>
       <c r="B36" t="n">
-        <v>57945</v>
+        <v>57948</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4385,16 +4385,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4417,10 +4417,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>760153</v>
+        <v>759783</v>
       </c>
       <c r="R36" t="n">
-        <v>7177247</v>
+        <v>7177071</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4457,14 +4457,14 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>hack i rotben på gran</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG36" t="b">
         <v>0</v>
@@ -4484,42 +4484,42 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132498962</v>
+        <v>132497587</v>
       </c>
       <c r="B37" t="n">
-        <v>99098</v>
+        <v>57948</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4527,10 +4527,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>760052</v>
+        <v>759611</v>
       </c>
       <c r="R37" t="n">
-        <v>7177092</v>
+        <v>7177137</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4565,13 +4565,17 @@
           <t>2026-04-14</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF37" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4590,42 +4594,42 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132497587</v>
+        <v>132498962</v>
       </c>
       <c r="B38" t="n">
-        <v>57948</v>
+        <v>99098</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4633,10 +4637,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>759611</v>
+        <v>760052</v>
       </c>
       <c r="R38" t="n">
-        <v>7177137</v>
+        <v>7177092</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4671,17 +4675,13 @@
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5135,10 +5135,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132499349</v>
+        <v>132498451</v>
       </c>
       <c r="B43" t="n">
-        <v>79317</v>
+        <v>57948</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5146,32 +5146,29 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -5181,10 +5178,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>760200</v>
+        <v>759745</v>
       </c>
       <c r="R43" t="n">
-        <v>7177185</v>
+        <v>7177069</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5221,16 +5218,15 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>fertil!</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF43" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5249,10 +5245,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132498451</v>
+        <v>132499017</v>
       </c>
       <c r="B44" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5260,31 +5256,30 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5292,10 +5287,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>759745</v>
+        <v>760089</v>
       </c>
       <c r="R44" t="n">
-        <v>7177069</v>
+        <v>7177139</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5330,17 +5325,13 @@
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5359,7 +5350,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132499017</v>
+        <v>132499349</v>
       </c>
       <c r="B45" t="n">
         <v>79317</v>
@@ -5393,7 +5384,11 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5401,10 +5396,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>760089</v>
+        <v>760200</v>
       </c>
       <c r="R45" t="n">
-        <v>7177139</v>
+        <v>7177185</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5437,6 +5432,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>fertil!</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 12578-2026 artfynd.xlsx
+++ b/artfynd/A 12578-2026 artfynd.xlsx
@@ -2858,10 +2858,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132499049</v>
+        <v>132499759</v>
       </c>
       <c r="B22" t="n">
-        <v>92316</v>
+        <v>91855</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2869,21 +2869,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4217</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>760133</v>
+        <v>759982</v>
       </c>
       <c r="R22" t="n">
-        <v>7177146</v>
+        <v>7177151</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2968,42 +2968,41 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132498370</v>
+        <v>132499049</v>
       </c>
       <c r="B23" t="n">
-        <v>57948</v>
+        <v>92316</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>4217</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3011,10 +3010,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>759732</v>
+        <v>760133</v>
       </c>
       <c r="R23" t="n">
-        <v>7177063</v>
+        <v>7177146</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3051,7 +3050,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>färska ringhack på grov tall</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3060,6 +3059,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3078,41 +3078,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132499759</v>
+        <v>132498370</v>
       </c>
       <c r="B24" t="n">
-        <v>91855</v>
+        <v>57948</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3120,10 +3121,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>759982</v>
+        <v>759732</v>
       </c>
       <c r="R24" t="n">
-        <v>7177151</v>
+        <v>7177063</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3160,7 +3161,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>färska ringhack på grov tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3169,7 +3170,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -4054,7 +4054,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132499169</v>
+        <v>132499026</v>
       </c>
       <c r="B33" t="n">
         <v>79317</v>
@@ -4096,10 +4096,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>760150</v>
+        <v>760140</v>
       </c>
       <c r="R33" t="n">
-        <v>7177131</v>
+        <v>7177159</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4159,10 +4159,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132499730</v>
+        <v>132498603</v>
       </c>
       <c r="B34" t="n">
-        <v>57945</v>
+        <v>57948</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4170,16 +4170,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4202,10 +4202,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>760153</v>
+        <v>759783</v>
       </c>
       <c r="R34" t="n">
-        <v>7177247</v>
+        <v>7177071</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4242,14 +4242,14 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>hack i rotben på gran</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG34" t="b">
         <v>0</v>
@@ -4269,7 +4269,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132499026</v>
+        <v>132499169</v>
       </c>
       <c r="B35" t="n">
         <v>79317</v>
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>760140</v>
+        <v>760150</v>
       </c>
       <c r="R35" t="n">
-        <v>7177159</v>
+        <v>7177131</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4374,10 +4374,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132498603</v>
+        <v>132499730</v>
       </c>
       <c r="B36" t="n">
-        <v>57948</v>
+        <v>57945</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4385,16 +4385,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4417,10 +4417,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>759783</v>
+        <v>760153</v>
       </c>
       <c r="R36" t="n">
-        <v>7177071</v>
+        <v>7177247</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4457,14 +4457,14 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>hack i rotben på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="b">
         <v>0</v>
@@ -4484,42 +4484,42 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132497587</v>
+        <v>132498962</v>
       </c>
       <c r="B37" t="n">
-        <v>57948</v>
+        <v>99098</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4527,10 +4527,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>759611</v>
+        <v>760052</v>
       </c>
       <c r="R37" t="n">
-        <v>7177137</v>
+        <v>7177092</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4565,17 +4565,13 @@
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4594,42 +4590,42 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132498962</v>
+        <v>132497587</v>
       </c>
       <c r="B38" t="n">
-        <v>99098</v>
+        <v>57948</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4637,10 +4633,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>760052</v>
+        <v>759611</v>
       </c>
       <c r="R38" t="n">
-        <v>7177092</v>
+        <v>7177137</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4675,13 +4671,17 @@
           <t>2026-04-14</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF38" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5135,10 +5135,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132498451</v>
+        <v>132499349</v>
       </c>
       <c r="B43" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5146,29 +5146,32 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -5178,10 +5181,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>759745</v>
+        <v>760200</v>
       </c>
       <c r="R43" t="n">
-        <v>7177069</v>
+        <v>7177185</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5218,15 +5221,16 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>fertil!</t>
         </is>
       </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5245,10 +5249,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132499017</v>
+        <v>132498451</v>
       </c>
       <c r="B44" t="n">
-        <v>79317</v>
+        <v>57948</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5256,30 +5260,31 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5287,10 +5292,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>760089</v>
+        <v>759745</v>
       </c>
       <c r="R44" t="n">
-        <v>7177139</v>
+        <v>7177069</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5325,13 +5330,17 @@
           <t>2026-04-14</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF44" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5350,7 +5359,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132499349</v>
+        <v>132499017</v>
       </c>
       <c r="B45" t="n">
         <v>79317</v>
@@ -5384,11 +5393,7 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5396,10 +5401,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>760200</v>
+        <v>760089</v>
       </c>
       <c r="R45" t="n">
-        <v>7177185</v>
+        <v>7177139</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5432,11 +5437,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>fertil!</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 12578-2026 artfynd.xlsx
+++ b/artfynd/A 12578-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132499893</v>
       </c>
       <c r="B2" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>132498057</v>
       </c>
       <c r="B3" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132498270</v>
+        <v>132498140</v>
       </c>
       <c r="B4" t="n">
-        <v>57945</v>
+        <v>57949</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,16 +906,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>759727</v>
+        <v>759709</v>
       </c>
       <c r="R4" t="n">
-        <v>7177084</v>
+        <v>7177110</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,14 +978,14 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>färska hål hackade i gran</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG4" t="b">
         <v>0</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132498877</v>
+        <v>132498270</v>
       </c>
       <c r="B5" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>760054</v>
+        <v>759727</v>
       </c>
       <c r="R5" t="n">
-        <v>7177088</v>
+        <v>7177084</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>hack på gran</t>
+          <t>färska hål hackade i gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132498140</v>
+        <v>132498877</v>
       </c>
       <c r="B6" t="n">
-        <v>57948</v>
+        <v>57946</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1126,16 +1126,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>759709</v>
+        <v>760054</v>
       </c>
       <c r="R6" t="n">
-        <v>7177110</v>
+        <v>7177088</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,14 +1198,14 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>hack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="b">
         <v>0</v>
@@ -1228,7 +1228,7 @@
         <v>132499583</v>
       </c>
       <c r="B7" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,42 +1335,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132498977</v>
+        <v>132497859</v>
       </c>
       <c r="B8" t="n">
-        <v>57948</v>
+        <v>99106</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1378,10 +1378,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>760051</v>
+        <v>759662</v>
       </c>
       <c r="R8" t="n">
-        <v>7177103</v>
+        <v>7177107</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,17 +1416,13 @@
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1445,42 +1441,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132497859</v>
+        <v>132497934</v>
       </c>
       <c r="B9" t="n">
-        <v>99098</v>
+        <v>57946</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1488,10 +1484,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>759662</v>
+        <v>759675</v>
       </c>
       <c r="R9" t="n">
-        <v>7177107</v>
+        <v>7177093</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1526,13 +1522,17 @@
           <t>2026-04-14</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>bohål i ihålig asp</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1551,10 +1551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132497762</v>
+        <v>132498977</v>
       </c>
       <c r="B10" t="n">
-        <v>79317</v>
+        <v>57949</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1562,30 +1562,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1593,10 +1594,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>759618</v>
+        <v>760051</v>
       </c>
       <c r="R10" t="n">
-        <v>7177137</v>
+        <v>7177103</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1631,13 +1632,17 @@
           <t>2026-04-14</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1656,10 +1661,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132497934</v>
+        <v>132497762</v>
       </c>
       <c r="B11" t="n">
-        <v>57945</v>
+        <v>79319</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1667,31 +1672,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1699,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>759675</v>
+        <v>759618</v>
       </c>
       <c r="R11" t="n">
-        <v>7177093</v>
+        <v>7177137</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1737,17 +1741,13 @@
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>bohål i ihålig asp</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1769,7 +1769,7 @@
         <v>132499783</v>
       </c>
       <c r="B12" t="n">
-        <v>91906</v>
+        <v>91912</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1876,10 +1876,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132497489</v>
+        <v>132499553</v>
       </c>
       <c r="B13" t="n">
-        <v>57948</v>
+        <v>79319</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,31 +1887,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1919,10 +1918,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>759600</v>
+        <v>760162</v>
       </c>
       <c r="R13" t="n">
-        <v>7177122</v>
+        <v>7177226</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1959,15 +1958,16 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>rikligt!</t>
         </is>
       </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1986,10 +1986,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132499553</v>
+        <v>132497489</v>
       </c>
       <c r="B14" t="n">
-        <v>79317</v>
+        <v>57949</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1997,30 +1997,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2028,10 +2029,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>760162</v>
+        <v>759600</v>
       </c>
       <c r="R14" t="n">
-        <v>7177226</v>
+        <v>7177122</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2068,16 +2069,15 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>rikligt!</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2096,10 +2096,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132499435</v>
+        <v>132498224</v>
       </c>
       <c r="B15" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2138,10 +2138,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>760203</v>
+        <v>759715</v>
       </c>
       <c r="R15" t="n">
-        <v>7177187</v>
+        <v>7177096</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2174,11 +2174,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>rikligt på gamla granar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2206,10 +2201,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132498224</v>
+        <v>132499435</v>
       </c>
       <c r="B16" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2248,10 +2243,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>759715</v>
+        <v>760203</v>
       </c>
       <c r="R16" t="n">
-        <v>7177096</v>
+        <v>7177187</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2284,6 +2279,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>rikligt på gamla granar</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2314,7 +2314,7 @@
         <v>132498323</v>
       </c>
       <c r="B17" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>132498725</v>
       </c>
       <c r="B18" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2531,10 +2531,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132498999</v>
+        <v>132498407</v>
       </c>
       <c r="B19" t="n">
-        <v>57948</v>
+        <v>91898</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2542,31 +2542,30 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2574,10 +2573,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>760075</v>
+        <v>759734</v>
       </c>
       <c r="R19" t="n">
-        <v>7177098</v>
+        <v>7177063</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2612,17 +2611,13 @@
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2641,10 +2636,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132498407</v>
+        <v>132498999</v>
       </c>
       <c r="B20" t="n">
-        <v>91892</v>
+        <v>57949</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2652,30 +2647,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2683,10 +2679,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>759734</v>
+        <v>760075</v>
       </c>
       <c r="R20" t="n">
-        <v>7177063</v>
+        <v>7177098</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2721,13 +2717,17 @@
           <t>2026-04-14</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2861,7 +2861,7 @@
         <v>132499759</v>
       </c>
       <c r="B22" t="n">
-        <v>91855</v>
+        <v>91861</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>132499049</v>
       </c>
       <c r="B23" t="n">
-        <v>92316</v>
+        <v>92322</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>132498370</v>
       </c>
       <c r="B24" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>132499331</v>
       </c>
       <c r="B25" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>132498179</v>
       </c>
       <c r="B26" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>132499748</v>
       </c>
       <c r="B27" t="n">
-        <v>89277</v>
+        <v>89283</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>132497957</v>
       </c>
       <c r="B28" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3618,42 +3618,42 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132497833</v>
+        <v>132498470</v>
       </c>
       <c r="B29" t="n">
-        <v>99098</v>
+        <v>57949</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3661,10 +3661,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>759652</v>
+        <v>759751</v>
       </c>
       <c r="R29" t="n">
-        <v>7177116</v>
+        <v>7177068</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3699,13 +3699,17 @@
           <t>2026-04-14</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3724,10 +3728,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132498470</v>
+        <v>132499673</v>
       </c>
       <c r="B30" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3767,10 +3771,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>759751</v>
+        <v>760160</v>
       </c>
       <c r="R30" t="n">
-        <v>7177068</v>
+        <v>7177228</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3807,7 +3811,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>barksprätt på två granar</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3834,42 +3838,42 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132499673</v>
+        <v>132497833</v>
       </c>
       <c r="B31" t="n">
-        <v>57948</v>
+        <v>99106</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3877,10 +3881,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>760160</v>
+        <v>759652</v>
       </c>
       <c r="R31" t="n">
-        <v>7177228</v>
+        <v>7177116</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3915,17 +3919,13 @@
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>barksprätt på två granar</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3944,10 +3944,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132497438</v>
+        <v>132499026</v>
       </c>
       <c r="B32" t="n">
-        <v>57948</v>
+        <v>79319</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3955,31 +3955,30 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3987,10 +3986,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>759602</v>
+        <v>760140</v>
       </c>
       <c r="R32" t="n">
-        <v>7177096</v>
+        <v>7177159</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4025,17 +4024,13 @@
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>barksprätt på två granar</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4054,10 +4049,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132499026</v>
+        <v>132499169</v>
       </c>
       <c r="B33" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4096,10 +4091,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>760140</v>
+        <v>760150</v>
       </c>
       <c r="R33" t="n">
-        <v>7177159</v>
+        <v>7177131</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4159,10 +4154,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132498603</v>
+        <v>132499730</v>
       </c>
       <c r="B34" t="n">
-        <v>57948</v>
+        <v>57946</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4170,16 +4165,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4202,10 +4197,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>759783</v>
+        <v>760153</v>
       </c>
       <c r="R34" t="n">
-        <v>7177071</v>
+        <v>7177247</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4242,14 +4237,14 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>hack i rotben på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="b">
         <v>0</v>
@@ -4269,10 +4264,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132499169</v>
+        <v>132498603</v>
       </c>
       <c r="B35" t="n">
-        <v>79317</v>
+        <v>57949</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4280,30 +4275,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4311,10 +4307,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>760150</v>
+        <v>759783</v>
       </c>
       <c r="R35" t="n">
-        <v>7177131</v>
+        <v>7177071</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4349,13 +4345,17 @@
           <t>2026-04-14</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF35" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4374,10 +4374,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132499730</v>
+        <v>132497438</v>
       </c>
       <c r="B36" t="n">
-        <v>57945</v>
+        <v>57949</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4385,16 +4385,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4417,10 +4417,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>760153</v>
+        <v>759602</v>
       </c>
       <c r="R36" t="n">
-        <v>7177247</v>
+        <v>7177096</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4457,14 +4457,14 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>hack i rotben på gran</t>
+          <t>barksprätt på två granar</t>
         </is>
       </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG36" t="b">
         <v>0</v>
@@ -4484,42 +4484,42 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132498962</v>
+        <v>132497587</v>
       </c>
       <c r="B37" t="n">
-        <v>99098</v>
+        <v>57949</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4527,10 +4527,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>760052</v>
+        <v>759611</v>
       </c>
       <c r="R37" t="n">
-        <v>7177092</v>
+        <v>7177137</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4565,13 +4565,17 @@
           <t>2026-04-14</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF37" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4590,42 +4594,42 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132497587</v>
+        <v>132498962</v>
       </c>
       <c r="B38" t="n">
-        <v>57948</v>
+        <v>99106</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4633,10 +4637,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>759611</v>
+        <v>760052</v>
       </c>
       <c r="R38" t="n">
-        <v>7177137</v>
+        <v>7177092</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4671,17 +4675,13 @@
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4700,10 +4700,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132499538</v>
+        <v>132499836</v>
       </c>
       <c r="B39" t="n">
-        <v>57945</v>
+        <v>92197</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4711,31 +4711,30 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4743,10 +4742,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>760162</v>
+        <v>759978</v>
       </c>
       <c r="R39" t="n">
-        <v>7177226</v>
+        <v>7177164</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4781,17 +4780,13 @@
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>hack i död ved</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4810,10 +4805,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132499504</v>
+        <v>132499538</v>
       </c>
       <c r="B40" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4853,10 +4848,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>760170</v>
+        <v>760162</v>
       </c>
       <c r="R40" t="n">
-        <v>7177214</v>
+        <v>7177226</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4893,7 +4888,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>hack i död gran</t>
+          <t>hack i död ved</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4920,10 +4915,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132499836</v>
+        <v>132498898</v>
       </c>
       <c r="B41" t="n">
-        <v>92191</v>
+        <v>57946</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4931,30 +4926,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4962,10 +4958,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>759978</v>
+        <v>760051</v>
       </c>
       <c r="R41" t="n">
-        <v>7177164</v>
+        <v>7177089</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5000,13 +4996,17 @@
           <t>2026-04-14</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>hack i död gran</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5025,10 +5025,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132498898</v>
+        <v>132499504</v>
       </c>
       <c r="B42" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5068,10 +5068,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>760051</v>
+        <v>760170</v>
       </c>
       <c r="R42" t="n">
-        <v>7177089</v>
+        <v>7177214</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5138,7 +5138,7 @@
         <v>132499349</v>
       </c>
       <c r="B43" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5249,10 +5249,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132498451</v>
+        <v>132499017</v>
       </c>
       <c r="B44" t="n">
-        <v>57948</v>
+        <v>79319</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5260,31 +5260,30 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5292,10 +5291,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>759745</v>
+        <v>760089</v>
       </c>
       <c r="R44" t="n">
-        <v>7177069</v>
+        <v>7177139</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5330,17 +5329,13 @@
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5359,10 +5354,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132499017</v>
+        <v>132498451</v>
       </c>
       <c r="B45" t="n">
-        <v>79317</v>
+        <v>57949</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5370,30 +5365,31 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5401,10 +5397,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>760089</v>
+        <v>759745</v>
       </c>
       <c r="R45" t="n">
-        <v>7177139</v>
+        <v>7177069</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5439,13 +5435,17 @@
           <t>2026-04-14</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF45" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5464,42 +5464,42 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132498541</v>
+        <v>132498655</v>
       </c>
       <c r="B46" t="n">
-        <v>99098</v>
+        <v>57949</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5507,10 +5507,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>759757</v>
+        <v>759879</v>
       </c>
       <c r="R46" t="n">
-        <v>7177076</v>
+        <v>7177034</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5547,16 +5547,15 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>ca 1 x 0,3 m med bladrosetter</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF46" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5575,42 +5574,42 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132498655</v>
+        <v>132498541</v>
       </c>
       <c r="B47" t="n">
-        <v>57948</v>
+        <v>99106</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5618,10 +5617,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>759879</v>
+        <v>759757</v>
       </c>
       <c r="R47" t="n">
-        <v>7177034</v>
+        <v>7177076</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5658,15 +5657,16 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>ca 1 x 0,3 m med bladrosetter</t>
         </is>
       </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12578-2026 artfynd.xlsx
+++ b/artfynd/A 12578-2026 artfynd.xlsx
@@ -2858,10 +2858,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132499759</v>
+        <v>132499049</v>
       </c>
       <c r="B22" t="n">
-        <v>91861</v>
+        <v>92322</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2869,21 +2869,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>4217</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759982</v>
+        <v>760133</v>
       </c>
       <c r="R22" t="n">
-        <v>7177151</v>
+        <v>7177146</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2968,10 +2968,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132499049</v>
+        <v>132499759</v>
       </c>
       <c r="B23" t="n">
-        <v>92322</v>
+        <v>91861</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2979,21 +2979,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4217</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3010,10 +3010,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>760133</v>
+        <v>759982</v>
       </c>
       <c r="R23" t="n">
-        <v>7177146</v>
+        <v>7177151</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 12578-2026 artfynd.xlsx
+++ b/artfynd/A 12578-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132499893</v>
+        <v>132498057</v>
       </c>
       <c r="B2" t="n">
-        <v>57946</v>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>759943</v>
+        <v>759701</v>
       </c>
       <c r="R2" t="n">
-        <v>7177168</v>
+        <v>7177107</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,14 +758,14 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>hack i död ved</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132498057</v>
+        <v>132499893</v>
       </c>
       <c r="B3" t="n">
-        <v>57949</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,16 +796,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>759701</v>
+        <v>759943</v>
       </c>
       <c r="R3" t="n">
-        <v>7177107</v>
+        <v>7177168</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,14 +868,14 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>hack i död ved</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
@@ -898,7 +898,7 @@
         <v>132498140</v>
       </c>
       <c r="B4" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>132498270</v>
       </c>
       <c r="B5" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>132498877</v>
       </c>
       <c r="B6" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>132499583</v>
       </c>
       <c r="B7" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,42 +1335,41 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132497859</v>
+        <v>132497762</v>
       </c>
       <c r="B8" t="n">
-        <v>99106</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1378,10 +1377,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>759662</v>
+        <v>759618</v>
       </c>
       <c r="R8" t="n">
-        <v>7177107</v>
+        <v>7177137</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1441,10 +1440,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132497934</v>
+        <v>132498977</v>
       </c>
       <c r="B9" t="n">
-        <v>57946</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1452,16 +1451,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1484,10 +1483,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>759675</v>
+        <v>760051</v>
       </c>
       <c r="R9" t="n">
-        <v>7177093</v>
+        <v>7177103</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,14 +1523,14 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>bohål i ihålig asp</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG9" t="b">
         <v>0</v>
@@ -1551,42 +1550,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132498977</v>
+        <v>132497859</v>
       </c>
       <c r="B10" t="n">
-        <v>57949</v>
+        <v>99116</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1594,10 +1593,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>760051</v>
+        <v>759662</v>
       </c>
       <c r="R10" t="n">
-        <v>7177103</v>
+        <v>7177107</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1632,17 +1631,13 @@
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1661,10 +1656,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132497762</v>
+        <v>132497934</v>
       </c>
       <c r="B11" t="n">
-        <v>79319</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1672,30 +1667,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1703,10 +1699,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>759618</v>
+        <v>759675</v>
       </c>
       <c r="R11" t="n">
-        <v>7177137</v>
+        <v>7177093</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1741,13 +1737,17 @@
           <t>2026-04-14</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>bohål i ihålig asp</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1769,7 +1769,7 @@
         <v>132499783</v>
       </c>
       <c r="B12" t="n">
-        <v>91912</v>
+        <v>91922</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>132499553</v>
       </c>
       <c r="B13" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>132497489</v>
       </c>
       <c r="B14" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>132498224</v>
       </c>
       <c r="B15" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>132499435</v>
       </c>
       <c r="B16" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2311,10 +2311,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132498323</v>
+        <v>132498725</v>
       </c>
       <c r="B17" t="n">
-        <v>57946</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2322,16 +2322,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2354,10 +2354,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>759721</v>
+        <v>759984</v>
       </c>
       <c r="R17" t="n">
-        <v>7177076</v>
+        <v>7177051</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2394,14 +2394,14 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>hack i basen på död gran</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG17" t="b">
         <v>0</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132498725</v>
+        <v>132498323</v>
       </c>
       <c r="B18" t="n">
-        <v>57949</v>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2432,16 +2432,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2464,10 +2464,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>759984</v>
+        <v>759721</v>
       </c>
       <c r="R18" t="n">
-        <v>7177051</v>
+        <v>7177076</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2504,14 +2504,14 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>hack i basen på död gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="b">
         <v>0</v>
@@ -2534,7 +2534,7 @@
         <v>132498407</v>
       </c>
       <c r="B19" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>132498999</v>
       </c>
       <c r="B20" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>132499049</v>
       </c>
       <c r="B22" t="n">
-        <v>92322</v>
+        <v>92332</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>132499759</v>
       </c>
       <c r="B23" t="n">
-        <v>91861</v>
+        <v>91871</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>132498370</v>
       </c>
       <c r="B24" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>132499331</v>
       </c>
       <c r="B25" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>132498179</v>
       </c>
       <c r="B26" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>132499748</v>
       </c>
       <c r="B27" t="n">
-        <v>89283</v>
+        <v>89291</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>132497957</v>
       </c>
       <c r="B28" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>132498470</v>
       </c>
       <c r="B29" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>132499673</v>
       </c>
       <c r="B30" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>132497833</v>
       </c>
       <c r="B31" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3944,10 +3944,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132499026</v>
+        <v>132498603</v>
       </c>
       <c r="B32" t="n">
-        <v>79319</v>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3955,30 +3955,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3986,10 +3987,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>760140</v>
+        <v>759783</v>
       </c>
       <c r="R32" t="n">
-        <v>7177159</v>
+        <v>7177071</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4024,13 +4025,17 @@
           <t>2026-04-14</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF32" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4049,10 +4054,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132499169</v>
+        <v>132497438</v>
       </c>
       <c r="B33" t="n">
-        <v>79319</v>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4060,30 +4065,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4091,10 +4097,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>760150</v>
+        <v>759602</v>
       </c>
       <c r="R33" t="n">
-        <v>7177131</v>
+        <v>7177096</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4129,13 +4135,17 @@
           <t>2026-04-14</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>barksprätt på två granar</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF33" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4154,10 +4164,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132499730</v>
+        <v>132499026</v>
       </c>
       <c r="B34" t="n">
-        <v>57946</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4165,31 +4175,30 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4197,10 +4206,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>760153</v>
+        <v>760140</v>
       </c>
       <c r="R34" t="n">
-        <v>7177247</v>
+        <v>7177159</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4235,17 +4244,13 @@
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>hack i rotben på gran</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4264,10 +4269,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132498603</v>
+        <v>132499169</v>
       </c>
       <c r="B35" t="n">
-        <v>57949</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4275,31 +4280,30 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4307,10 +4311,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>759783</v>
+        <v>760150</v>
       </c>
       <c r="R35" t="n">
-        <v>7177071</v>
+        <v>7177131</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4345,17 +4349,13 @@
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4374,10 +4374,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132497438</v>
+        <v>132499730</v>
       </c>
       <c r="B36" t="n">
-        <v>57949</v>
+        <v>57950</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4385,16 +4385,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4417,10 +4417,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>759602</v>
+        <v>760153</v>
       </c>
       <c r="R36" t="n">
-        <v>7177096</v>
+        <v>7177247</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4457,14 +4457,14 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>barksprätt på två granar</t>
+          <t>hack i rotben på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="b">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>132497587</v>
       </c>
       <c r="B37" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>132498962</v>
       </c>
       <c r="B38" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4700,10 +4700,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132499836</v>
+        <v>132499538</v>
       </c>
       <c r="B39" t="n">
-        <v>92197</v>
+        <v>57950</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4711,30 +4711,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4742,10 +4743,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>759978</v>
+        <v>760162</v>
       </c>
       <c r="R39" t="n">
-        <v>7177164</v>
+        <v>7177226</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4780,13 +4781,17 @@
           <t>2026-04-14</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>hack i död ved</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4805,10 +4810,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132499538</v>
+        <v>132498898</v>
       </c>
       <c r="B40" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4848,10 +4853,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>760162</v>
+        <v>760051</v>
       </c>
       <c r="R40" t="n">
-        <v>7177226</v>
+        <v>7177089</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4888,7 +4893,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>hack i död ved</t>
+          <t>hack i död gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4915,10 +4920,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132498898</v>
+        <v>132499504</v>
       </c>
       <c r="B41" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4958,10 +4963,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>760051</v>
+        <v>760170</v>
       </c>
       <c r="R41" t="n">
-        <v>7177089</v>
+        <v>7177214</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5025,10 +5030,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132499504</v>
+        <v>132499836</v>
       </c>
       <c r="B42" t="n">
-        <v>57946</v>
+        <v>92207</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5036,31 +5041,30 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5068,10 +5072,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>760170</v>
+        <v>759978</v>
       </c>
       <c r="R42" t="n">
-        <v>7177214</v>
+        <v>7177164</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5106,17 +5110,13 @@
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>hack i död gran</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5135,10 +5135,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132499349</v>
+        <v>132498451</v>
       </c>
       <c r="B43" t="n">
-        <v>79319</v>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5146,32 +5146,29 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -5181,10 +5178,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>760200</v>
+        <v>759745</v>
       </c>
       <c r="R43" t="n">
-        <v>7177185</v>
+        <v>7177069</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5221,16 +5218,15 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>fertil!</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF43" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5252,7 +5248,7 @@
         <v>132499017</v>
       </c>
       <c r="B44" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5354,10 +5350,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132498451</v>
+        <v>132499349</v>
       </c>
       <c r="B45" t="n">
-        <v>57949</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5365,29 +5361,32 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -5397,10 +5396,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>759745</v>
+        <v>760200</v>
       </c>
       <c r="R45" t="n">
-        <v>7177069</v>
+        <v>7177185</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5437,15 +5436,16 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>fertil!</t>
         </is>
       </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5467,7 +5467,7 @@
         <v>132498655</v>
       </c>
       <c r="B46" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>132498541</v>
       </c>
       <c r="B47" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 12578-2026 artfynd.xlsx
+++ b/artfynd/A 12578-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132498057</v>
+        <v>132499893</v>
       </c>
       <c r="B2" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>759701</v>
+        <v>759943</v>
       </c>
       <c r="R2" t="n">
-        <v>7177107</v>
+        <v>7177168</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,14 +758,14 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>hack i död ved</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132499893</v>
+        <v>132498057</v>
       </c>
       <c r="B3" t="n">
-        <v>57950</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,16 +796,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>759943</v>
+        <v>759701</v>
       </c>
       <c r="R3" t="n">
-        <v>7177168</v>
+        <v>7177107</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,14 +868,14 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>hack i död ved</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132497762</v>
+        <v>132498977</v>
       </c>
       <c r="B8" t="n">
-        <v>79327</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1346,30 +1346,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1377,10 +1378,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>759618</v>
+        <v>760051</v>
       </c>
       <c r="R8" t="n">
-        <v>7177137</v>
+        <v>7177103</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,13 +1416,17 @@
           <t>2026-04-14</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1440,42 +1445,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132498977</v>
+        <v>132497859</v>
       </c>
       <c r="B9" t="n">
-        <v>57953</v>
+        <v>99117</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1483,10 +1488,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>760051</v>
+        <v>759662</v>
       </c>
       <c r="R9" t="n">
-        <v>7177103</v>
+        <v>7177107</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,17 +1526,13 @@
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1550,42 +1551,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132497859</v>
+        <v>132497934</v>
       </c>
       <c r="B10" t="n">
-        <v>99116</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1593,10 +1594,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>759662</v>
+        <v>759675</v>
       </c>
       <c r="R10" t="n">
-        <v>7177107</v>
+        <v>7177093</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1631,13 +1632,17 @@
           <t>2026-04-14</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>bohål i ihålig asp</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1656,10 +1661,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132497934</v>
+        <v>132499783</v>
       </c>
       <c r="B11" t="n">
-        <v>57950</v>
+        <v>91923</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1667,31 +1672,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1699,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>759675</v>
+        <v>759979</v>
       </c>
       <c r="R11" t="n">
-        <v>7177093</v>
+        <v>7177157</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1739,7 +1743,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>bohål i ihålig asp</t>
+          <t>under en gammal, mossbelupen, grov granlåga</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1748,6 +1752,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1766,10 +1771,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132499783</v>
+        <v>132497762</v>
       </c>
       <c r="B12" t="n">
-        <v>91922</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1777,27 +1782,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1808,10 +1813,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>759979</v>
+        <v>759618</v>
       </c>
       <c r="R12" t="n">
-        <v>7177157</v>
+        <v>7177137</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1844,11 +1849,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>under en gammal, mossbelupen, grov granlåga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1876,10 +1876,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132499553</v>
+        <v>132497489</v>
       </c>
       <c r="B13" t="n">
-        <v>79327</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,30 +1887,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1918,10 +1919,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>760162</v>
+        <v>759600</v>
       </c>
       <c r="R13" t="n">
-        <v>7177226</v>
+        <v>7177122</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1958,16 +1959,15 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>rikligt!</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1986,10 +1986,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132497489</v>
+        <v>132499553</v>
       </c>
       <c r="B14" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1997,31 +1997,30 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2029,10 +2028,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>759600</v>
+        <v>760162</v>
       </c>
       <c r="R14" t="n">
-        <v>7177122</v>
+        <v>7177226</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2069,15 +2068,16 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>rikligt!</t>
         </is>
       </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2531,10 +2531,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132498407</v>
+        <v>132498999</v>
       </c>
       <c r="B19" t="n">
-        <v>91908</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2542,30 +2542,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2573,10 +2574,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>759734</v>
+        <v>760075</v>
       </c>
       <c r="R19" t="n">
-        <v>7177063</v>
+        <v>7177098</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2611,13 +2612,17 @@
           <t>2026-04-14</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2636,10 +2641,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132498999</v>
+        <v>132498407</v>
       </c>
       <c r="B20" t="n">
-        <v>57953</v>
+        <v>91909</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2647,31 +2652,30 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2679,10 +2683,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>760075</v>
+        <v>759734</v>
       </c>
       <c r="R20" t="n">
-        <v>7177098</v>
+        <v>7177063</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2717,17 +2721,13 @@
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2858,41 +2858,42 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132499049</v>
+        <v>132498370</v>
       </c>
       <c r="B22" t="n">
-        <v>92332</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4217</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2900,10 +2901,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>760133</v>
+        <v>759732</v>
       </c>
       <c r="R22" t="n">
-        <v>7177146</v>
+        <v>7177063</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2940,7 +2941,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>färska ringhack på grov tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2949,7 +2950,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2968,10 +2968,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132499759</v>
+        <v>132499049</v>
       </c>
       <c r="B23" t="n">
-        <v>91871</v>
+        <v>92333</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2979,21 +2979,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>4217</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3010,10 +3010,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>759982</v>
+        <v>760133</v>
       </c>
       <c r="R23" t="n">
-        <v>7177151</v>
+        <v>7177146</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3078,42 +3078,41 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132498370</v>
+        <v>132499759</v>
       </c>
       <c r="B24" t="n">
-        <v>57953</v>
+        <v>91872</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3121,10 +3120,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>759732</v>
+        <v>759982</v>
       </c>
       <c r="R24" t="n">
-        <v>7177063</v>
+        <v>7177151</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3161,7 +3160,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>färska ringhack på grov tall</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3170,6 +3169,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3406,7 +3406,7 @@
         <v>132499748</v>
       </c>
       <c r="B27" t="n">
-        <v>89291</v>
+        <v>89292</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>132497957</v>
       </c>
       <c r="B28" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>132497833</v>
       </c>
       <c r="B31" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3944,10 +3944,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132498603</v>
+        <v>132499026</v>
       </c>
       <c r="B32" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3955,31 +3955,30 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3987,10 +3986,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>759783</v>
+        <v>760140</v>
       </c>
       <c r="R32" t="n">
-        <v>7177071</v>
+        <v>7177159</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4025,17 +4024,13 @@
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4054,10 +4049,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132497438</v>
+        <v>132499169</v>
       </c>
       <c r="B33" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4065,31 +4060,30 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4097,10 +4091,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>759602</v>
+        <v>760150</v>
       </c>
       <c r="R33" t="n">
-        <v>7177096</v>
+        <v>7177131</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4135,17 +4129,13 @@
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>barksprätt på två granar</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4164,10 +4154,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132499026</v>
+        <v>132499730</v>
       </c>
       <c r="B34" t="n">
-        <v>79327</v>
+        <v>57950</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4175,30 +4165,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4206,10 +4197,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>760140</v>
+        <v>760153</v>
       </c>
       <c r="R34" t="n">
-        <v>7177159</v>
+        <v>7177247</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4244,13 +4235,17 @@
           <t>2026-04-14</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>hack i rotben på gran</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4269,10 +4264,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132499169</v>
+        <v>132498603</v>
       </c>
       <c r="B35" t="n">
-        <v>79327</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4280,30 +4275,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4311,10 +4307,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>760150</v>
+        <v>759783</v>
       </c>
       <c r="R35" t="n">
-        <v>7177131</v>
+        <v>7177071</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4349,13 +4345,17 @@
           <t>2026-04-14</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF35" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4374,10 +4374,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132499730</v>
+        <v>132497438</v>
       </c>
       <c r="B36" t="n">
-        <v>57950</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4385,16 +4385,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4417,10 +4417,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>760153</v>
+        <v>759602</v>
       </c>
       <c r="R36" t="n">
-        <v>7177247</v>
+        <v>7177096</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4457,14 +4457,14 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>hack i rotben på gran</t>
+          <t>barksprätt på två granar</t>
         </is>
       </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG36" t="b">
         <v>0</v>
@@ -4484,42 +4484,42 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132497587</v>
+        <v>132498962</v>
       </c>
       <c r="B37" t="n">
-        <v>57953</v>
+        <v>99117</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4527,10 +4527,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>759611</v>
+        <v>760052</v>
       </c>
       <c r="R37" t="n">
-        <v>7177137</v>
+        <v>7177092</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4565,17 +4565,13 @@
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4594,42 +4590,42 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132498962</v>
+        <v>132497587</v>
       </c>
       <c r="B38" t="n">
-        <v>99116</v>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4637,10 +4633,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>760052</v>
+        <v>759611</v>
       </c>
       <c r="R38" t="n">
-        <v>7177092</v>
+        <v>7177137</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4675,13 +4671,17 @@
           <t>2026-04-14</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF38" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4700,10 +4700,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132499538</v>
+        <v>132499836</v>
       </c>
       <c r="B39" t="n">
-        <v>57950</v>
+        <v>92208</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4711,31 +4711,30 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4743,10 +4742,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>760162</v>
+        <v>759978</v>
       </c>
       <c r="R39" t="n">
-        <v>7177226</v>
+        <v>7177164</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4781,17 +4780,13 @@
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>hack i död ved</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4810,7 +4805,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132498898</v>
+        <v>132499504</v>
       </c>
       <c r="B40" t="n">
         <v>57950</v>
@@ -4853,10 +4848,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>760051</v>
+        <v>760170</v>
       </c>
       <c r="R40" t="n">
-        <v>7177089</v>
+        <v>7177214</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4920,7 +4915,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132499504</v>
+        <v>132499538</v>
       </c>
       <c r="B41" t="n">
         <v>57950</v>
@@ -4963,10 +4958,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>760170</v>
+        <v>760162</v>
       </c>
       <c r="R41" t="n">
-        <v>7177214</v>
+        <v>7177226</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5003,7 +4998,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>hack i död gran</t>
+          <t>hack i död ved</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5030,10 +5025,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132499836</v>
+        <v>132498898</v>
       </c>
       <c r="B42" t="n">
-        <v>92207</v>
+        <v>57950</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5041,30 +5036,31 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5072,10 +5068,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>759978</v>
+        <v>760051</v>
       </c>
       <c r="R42" t="n">
-        <v>7177164</v>
+        <v>7177089</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5110,13 +5106,17 @@
           <t>2026-04-14</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>hack i död gran</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5135,10 +5135,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132498451</v>
+        <v>132499349</v>
       </c>
       <c r="B43" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5146,29 +5146,32 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -5178,10 +5181,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>759745</v>
+        <v>760200</v>
       </c>
       <c r="R43" t="n">
-        <v>7177069</v>
+        <v>7177185</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5218,15 +5221,16 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>fertil!</t>
         </is>
       </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5350,10 +5354,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132499349</v>
+        <v>132498451</v>
       </c>
       <c r="B45" t="n">
-        <v>79327</v>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5361,32 +5365,29 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -5396,10 +5397,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>760200</v>
+        <v>759745</v>
       </c>
       <c r="R45" t="n">
-        <v>7177185</v>
+        <v>7177069</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5436,16 +5437,15 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>fertil!</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF45" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5577,7 +5577,7 @@
         <v>132498541</v>
       </c>
       <c r="B47" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 12578-2026 artfynd.xlsx
+++ b/artfynd/A 12578-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132499893</v>
+        <v>132498057</v>
       </c>
       <c r="B2" t="n">
-        <v>57950</v>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>759943</v>
+        <v>759701</v>
       </c>
       <c r="R2" t="n">
-        <v>7177168</v>
+        <v>7177107</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,14 +758,14 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>hack i död ved</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132498057</v>
+        <v>132499893</v>
       </c>
       <c r="B3" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,16 +796,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>759701</v>
+        <v>759943</v>
       </c>
       <c r="R3" t="n">
-        <v>7177107</v>
+        <v>7177168</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,14 +868,14 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>hack i död ved</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132498140</v>
+        <v>132498270</v>
       </c>
       <c r="B4" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,16 +906,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>759709</v>
+        <v>759727</v>
       </c>
       <c r="R4" t="n">
-        <v>7177110</v>
+        <v>7177084</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,14 +978,14 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>färska hål hackade i gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="b">
         <v>0</v>
@@ -1005,7 +1005,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132498270</v>
+        <v>132498877</v>
       </c>
       <c r="B5" t="n">
         <v>57950</v>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>759727</v>
+        <v>760054</v>
       </c>
       <c r="R5" t="n">
-        <v>7177084</v>
+        <v>7177088</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>färska hål hackade i gran</t>
+          <t>hack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,7 +1115,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132498877</v>
+        <v>132499583</v>
       </c>
       <c r="B6" t="n">
         <v>57950</v>
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>760054</v>
+        <v>760164</v>
       </c>
       <c r="R6" t="n">
-        <v>7177088</v>
+        <v>7177226</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>hack på gran</t>
+          <t>hack i gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132499583</v>
+        <v>132498140</v>
       </c>
       <c r="B7" t="n">
-        <v>57950</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1236,16 +1236,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1268,10 +1268,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>760164</v>
+        <v>759709</v>
       </c>
       <c r="R7" t="n">
-        <v>7177226</v>
+        <v>7177110</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,14 +1308,14 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>hack i gran</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG7" t="b">
         <v>0</v>
@@ -1335,42 +1335,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132498977</v>
+        <v>132497859</v>
       </c>
       <c r="B8" t="n">
-        <v>57953</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1378,10 +1378,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>760051</v>
+        <v>759662</v>
       </c>
       <c r="R8" t="n">
-        <v>7177103</v>
+        <v>7177107</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,17 +1416,13 @@
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1445,42 +1441,41 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132497859</v>
+        <v>132497762</v>
       </c>
       <c r="B9" t="n">
-        <v>99117</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1488,10 +1483,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>759662</v>
+        <v>759618</v>
       </c>
       <c r="R9" t="n">
-        <v>7177107</v>
+        <v>7177137</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1551,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132497934</v>
+        <v>132499783</v>
       </c>
       <c r="B10" t="n">
-        <v>57950</v>
+        <v>91923</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1562,31 +1557,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1594,10 +1588,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>759675</v>
+        <v>759979</v>
       </c>
       <c r="R10" t="n">
-        <v>7177093</v>
+        <v>7177157</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,7 +1628,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>bohål i ihålig asp</t>
+          <t>under en gammal, mossbelupen, grov granlåga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1643,6 +1637,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1661,10 +1656,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132499783</v>
+        <v>132498977</v>
       </c>
       <c r="B11" t="n">
-        <v>91923</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1672,30 +1667,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1703,10 +1699,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>759979</v>
+        <v>760051</v>
       </c>
       <c r="R11" t="n">
-        <v>7177157</v>
+        <v>7177103</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,16 +1739,15 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>under en gammal, mossbelupen, grov granlåga</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1771,10 +1766,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132497762</v>
+        <v>132497934</v>
       </c>
       <c r="B12" t="n">
-        <v>79327</v>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1782,30 +1777,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1813,10 +1809,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>759618</v>
+        <v>759675</v>
       </c>
       <c r="R12" t="n">
-        <v>7177137</v>
+        <v>7177093</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1851,13 +1847,17 @@
           <t>2026-04-14</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>bohål i ihålig asp</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2311,10 +2311,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132498725</v>
+        <v>132498323</v>
       </c>
       <c r="B17" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2322,16 +2322,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2354,10 +2354,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>759984</v>
+        <v>759721</v>
       </c>
       <c r="R17" t="n">
-        <v>7177051</v>
+        <v>7177076</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2394,14 +2394,14 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>hack i basen på död gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="b">
         <v>0</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132498323</v>
+        <v>132498725</v>
       </c>
       <c r="B18" t="n">
-        <v>57950</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2432,16 +2432,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2464,10 +2464,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>759721</v>
+        <v>759984</v>
       </c>
       <c r="R18" t="n">
-        <v>7177076</v>
+        <v>7177051</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2504,14 +2504,14 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>hack i basen på död gran</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG18" t="b">
         <v>0</v>
@@ -2531,10 +2531,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132498999</v>
+        <v>132498407</v>
       </c>
       <c r="B19" t="n">
-        <v>57953</v>
+        <v>91909</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2542,31 +2542,30 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2574,10 +2573,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>760075</v>
+        <v>759734</v>
       </c>
       <c r="R19" t="n">
-        <v>7177098</v>
+        <v>7177063</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2612,17 +2611,13 @@
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2641,10 +2636,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132498407</v>
+        <v>132498999</v>
       </c>
       <c r="B20" t="n">
-        <v>91909</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2652,30 +2647,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2683,10 +2679,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>759734</v>
+        <v>760075</v>
       </c>
       <c r="R20" t="n">
-        <v>7177063</v>
+        <v>7177098</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2721,13 +2717,17 @@
           <t>2026-04-14</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3841,7 +3841,7 @@
         <v>132497833</v>
       </c>
       <c r="B31" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4154,10 +4154,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132499730</v>
+        <v>132498603</v>
       </c>
       <c r="B34" t="n">
-        <v>57950</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4165,16 +4165,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4197,10 +4197,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>760153</v>
+        <v>759783</v>
       </c>
       <c r="R34" t="n">
-        <v>7177247</v>
+        <v>7177071</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4237,14 +4237,14 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>hack i rotben på gran</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG34" t="b">
         <v>0</v>
@@ -4264,7 +4264,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132498603</v>
+        <v>132497438</v>
       </c>
       <c r="B35" t="n">
         <v>57953</v>
@@ -4307,10 +4307,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>759783</v>
+        <v>759602</v>
       </c>
       <c r="R35" t="n">
-        <v>7177071</v>
+        <v>7177096</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>barksprätt på två granar</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4374,10 +4374,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132497438</v>
+        <v>132499730</v>
       </c>
       <c r="B36" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4385,16 +4385,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4417,10 +4417,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>759602</v>
+        <v>760153</v>
       </c>
       <c r="R36" t="n">
-        <v>7177096</v>
+        <v>7177247</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4457,14 +4457,14 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>barksprätt på två granar</t>
+          <t>hack i rotben på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="b">
         <v>0</v>
@@ -4484,42 +4484,42 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132498962</v>
+        <v>132497587</v>
       </c>
       <c r="B37" t="n">
-        <v>99117</v>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4527,10 +4527,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>760052</v>
+        <v>759611</v>
       </c>
       <c r="R37" t="n">
-        <v>7177092</v>
+        <v>7177137</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4565,13 +4565,17 @@
           <t>2026-04-14</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF37" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4590,42 +4594,42 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132497587</v>
+        <v>132498962</v>
       </c>
       <c r="B38" t="n">
-        <v>57953</v>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4633,10 +4637,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>759611</v>
+        <v>760052</v>
       </c>
       <c r="R38" t="n">
-        <v>7177137</v>
+        <v>7177092</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4671,17 +4675,13 @@
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4700,10 +4700,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132499836</v>
+        <v>132499538</v>
       </c>
       <c r="B39" t="n">
-        <v>92208</v>
+        <v>57950</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4711,30 +4711,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4742,10 +4743,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>759978</v>
+        <v>760162</v>
       </c>
       <c r="R39" t="n">
-        <v>7177164</v>
+        <v>7177226</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4780,13 +4781,17 @@
           <t>2026-04-14</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>hack i död ved</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4805,7 +4810,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132499504</v>
+        <v>132498898</v>
       </c>
       <c r="B40" t="n">
         <v>57950</v>
@@ -4848,10 +4853,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>760170</v>
+        <v>760051</v>
       </c>
       <c r="R40" t="n">
-        <v>7177214</v>
+        <v>7177089</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4915,7 +4920,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132499538</v>
+        <v>132499504</v>
       </c>
       <c r="B41" t="n">
         <v>57950</v>
@@ -4958,10 +4963,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>760162</v>
+        <v>760170</v>
       </c>
       <c r="R41" t="n">
-        <v>7177226</v>
+        <v>7177214</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4998,7 +5003,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>hack i död ved</t>
+          <t>hack i död gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5025,10 +5030,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132498898</v>
+        <v>132499836</v>
       </c>
       <c r="B42" t="n">
-        <v>57950</v>
+        <v>92208</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5036,31 +5041,30 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5068,10 +5072,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>760051</v>
+        <v>759978</v>
       </c>
       <c r="R42" t="n">
-        <v>7177089</v>
+        <v>7177164</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5106,17 +5110,13 @@
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>hack i död gran</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5577,7 +5577,7 @@
         <v>132498541</v>
       </c>
       <c r="B47" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 12578-2026 artfynd.xlsx
+++ b/artfynd/A 12578-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AY56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132499893</v>
+        <v>132499748</v>
       </c>
       <c r="B2" t="n">
-        <v>57955</v>
+        <v>89354</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>759943</v>
+        <v>760175</v>
       </c>
       <c r="R2" t="n">
-        <v>7177168</v>
+        <v>7177177</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,7 +757,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>hack i död ved</t>
+          <t>på toppbruten gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,6 +766,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132498057</v>
+        <v>132499836</v>
       </c>
       <c r="B3" t="n">
-        <v>57958</v>
+        <v>92245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,31 +796,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -828,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>759701</v>
+        <v>759978</v>
       </c>
       <c r="R3" t="n">
-        <v>7177107</v>
+        <v>7177164</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,17 +865,13 @@
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -895,10 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132498270</v>
+        <v>132497957</v>
       </c>
       <c r="B4" t="n">
-        <v>57955</v>
+        <v>91974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,31 +901,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -938,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>759727</v>
+        <v>759681</v>
       </c>
       <c r="R4" t="n">
-        <v>7177084</v>
+        <v>7177101</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,17 +970,13 @@
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>färska hål hackade i gran</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1005,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132498877</v>
+        <v>132498407</v>
       </c>
       <c r="B5" t="n">
-        <v>57955</v>
+        <v>91974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,31 +1006,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1048,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>760054</v>
+        <v>759734</v>
       </c>
       <c r="R5" t="n">
-        <v>7177088</v>
+        <v>7177063</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,17 +1075,13 @@
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>hack på gran</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1115,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132499583</v>
+        <v>132498758</v>
       </c>
       <c r="B6" t="n">
-        <v>57955</v>
+        <v>91974</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1126,31 +1111,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1158,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>760164</v>
+        <v>759997</v>
       </c>
       <c r="R6" t="n">
-        <v>7177226</v>
+        <v>7177045</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,17 +1180,13 @@
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>hack i gran</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1225,42 +1205,41 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132498140</v>
+        <v>132499783</v>
       </c>
       <c r="B7" t="n">
-        <v>57958</v>
+        <v>91988</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1268,10 +1247,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>759709</v>
+        <v>759979</v>
       </c>
       <c r="R7" t="n">
-        <v>7177110</v>
+        <v>7177157</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,15 +1287,16 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>under en gammal, mossbelupen, grov granlåga</t>
         </is>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1335,38 +1315,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132497762</v>
+        <v>132499049</v>
       </c>
       <c r="B8" t="n">
-        <v>79333</v>
+        <v>92370</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1377,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>759618</v>
+        <v>760133</v>
       </c>
       <c r="R8" t="n">
-        <v>7177137</v>
+        <v>7177146</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,6 +1393,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1440,32 +1425,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132499783</v>
+        <v>132499759</v>
       </c>
       <c r="B9" t="n">
-        <v>91932</v>
+        <v>91937</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1482,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>759979</v>
+        <v>759982</v>
       </c>
       <c r="R9" t="n">
-        <v>7177157</v>
+        <v>7177151</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1522,7 +1507,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>under en gammal, mossbelupen, grov granlåga</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1550,10 +1535,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132497859</v>
+        <v>132497201</v>
       </c>
       <c r="B10" t="n">
-        <v>99130</v>
+        <v>79373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,31 +1546,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1593,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>759662</v>
+        <v>759591</v>
       </c>
       <c r="R10" t="n">
-        <v>7177107</v>
+        <v>7177039</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1656,42 +1640,41 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132497934</v>
+        <v>132497762</v>
       </c>
       <c r="B11" t="n">
-        <v>57955</v>
+        <v>79373</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1699,10 +1682,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>759675</v>
+        <v>759618</v>
       </c>
       <c r="R11" t="n">
-        <v>7177093</v>
+        <v>7177137</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1737,17 +1720,13 @@
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>bohål i ihålig asp</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1766,42 +1745,41 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132498977</v>
+        <v>132498179</v>
       </c>
       <c r="B12" t="n">
-        <v>57958</v>
+        <v>79373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1809,10 +1787,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>760051</v>
+        <v>759709</v>
       </c>
       <c r="R12" t="n">
-        <v>7177103</v>
+        <v>7177110</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1847,17 +1825,13 @@
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1876,14 +1850,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132499553</v>
+        <v>132498224</v>
       </c>
       <c r="B13" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1918,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>760162</v>
+        <v>759715</v>
       </c>
       <c r="R13" t="n">
-        <v>7177226</v>
+        <v>7177096</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1954,11 +1928,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>rikligt!</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1986,42 +1955,41 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132497489</v>
+        <v>132499017</v>
       </c>
       <c r="B14" t="n">
-        <v>57958</v>
+        <v>79373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2029,10 +1997,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>759600</v>
+        <v>760089</v>
       </c>
       <c r="R14" t="n">
-        <v>7177122</v>
+        <v>7177139</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2067,17 +2035,13 @@
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2096,14 +2060,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132498224</v>
+        <v>132499026</v>
       </c>
       <c r="B15" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2138,10 +2102,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>759715</v>
+        <v>760140</v>
       </c>
       <c r="R15" t="n">
-        <v>7177096</v>
+        <v>7177159</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2201,14 +2165,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132499435</v>
+        <v>132499169</v>
       </c>
       <c r="B16" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2243,10 +2207,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>760203</v>
+        <v>760150</v>
       </c>
       <c r="R16" t="n">
-        <v>7177187</v>
+        <v>7177131</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2279,11 +2243,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>rikligt på gamla granar</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2311,40 +2270,43 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132498725</v>
+        <v>132499349</v>
       </c>
       <c r="B17" t="n">
-        <v>57958</v>
+        <v>79373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2354,10 +2316,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>759984</v>
+        <v>760200</v>
       </c>
       <c r="R17" t="n">
-        <v>7177051</v>
+        <v>7177185</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2394,15 +2356,16 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>fertil!</t>
         </is>
       </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2421,42 +2384,41 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132498323</v>
+        <v>132499435</v>
       </c>
       <c r="B18" t="n">
-        <v>57955</v>
+        <v>79373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2464,10 +2426,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>759721</v>
+        <v>760203</v>
       </c>
       <c r="R18" t="n">
-        <v>7177076</v>
+        <v>7177187</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2504,7 +2466,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>hack i basen på död gran</t>
+          <t>rikligt på gamla granar</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2513,6 +2475,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2531,42 +2494,41 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132498999</v>
+        <v>132499553</v>
       </c>
       <c r="B19" t="n">
-        <v>57958</v>
+        <v>79373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2574,10 +2536,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>760075</v>
+        <v>760162</v>
       </c>
       <c r="R19" t="n">
-        <v>7177098</v>
+        <v>7177226</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2614,15 +2576,16 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>rikligt!</t>
         </is>
       </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2641,41 +2604,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132498407</v>
+        <v>132496824</v>
       </c>
       <c r="B20" t="n">
-        <v>91918</v>
+        <v>57972</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2683,10 +2647,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>759734</v>
+        <v>759588</v>
       </c>
       <c r="R20" t="n">
-        <v>7177063</v>
+        <v>7177031</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2721,13 +2685,17 @@
           <t>2026-04-14</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>färska hack i basen på gran</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2746,10 +2714,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132498686</v>
+        <v>132497934</v>
       </c>
       <c r="B21" t="n">
-        <v>5179</v>
+        <v>57972</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2757,30 +2725,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2790,10 +2757,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759893</v>
+        <v>759675</v>
       </c>
       <c r="R21" t="n">
-        <v>7177023</v>
+        <v>7177093</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2830,7 +2797,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>typiska gnagspår på gran</t>
+          <t>bohål i ihålig asp</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2839,7 +2806,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2858,27 +2824,27 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132498370</v>
+        <v>132498270</v>
       </c>
       <c r="B22" t="n">
-        <v>57958</v>
+        <v>57972</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2901,10 +2867,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759732</v>
+        <v>759727</v>
       </c>
       <c r="R22" t="n">
-        <v>7177063</v>
+        <v>7177084</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2941,7 +2907,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>färska ringhack på grov tall</t>
+          <t>färska hål hackade i gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2968,10 +2934,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132499049</v>
+        <v>132498323</v>
       </c>
       <c r="B23" t="n">
-        <v>92342</v>
+        <v>57972</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2979,30 +2945,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4217</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3010,10 +2977,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>760133</v>
+        <v>759721</v>
       </c>
       <c r="R23" t="n">
-        <v>7177146</v>
+        <v>7177076</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3050,7 +3017,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>hack i basen på död gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3059,7 +3026,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3078,10 +3044,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132499759</v>
+        <v>132498877</v>
       </c>
       <c r="B24" t="n">
-        <v>91881</v>
+        <v>57972</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3089,30 +3055,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3120,10 +3087,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>759982</v>
+        <v>760054</v>
       </c>
       <c r="R24" t="n">
-        <v>7177151</v>
+        <v>7177088</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3160,7 +3127,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>hack på gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3169,7 +3136,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3188,27 +3154,27 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132499331</v>
+        <v>132498898</v>
       </c>
       <c r="B25" t="n">
-        <v>57958</v>
+        <v>57972</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3231,10 +3197,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>760200</v>
+        <v>760051</v>
       </c>
       <c r="R25" t="n">
-        <v>7177185</v>
+        <v>7177089</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3271,14 +3237,14 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>hack i död gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="b">
         <v>0</v>
@@ -3298,41 +3264,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132498179</v>
+        <v>132499504</v>
       </c>
       <c r="B26" t="n">
-        <v>79333</v>
+        <v>57972</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3340,10 +3307,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>759709</v>
+        <v>760170</v>
       </c>
       <c r="R26" t="n">
-        <v>7177110</v>
+        <v>7177214</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3378,13 +3345,17 @@
           <t>2026-04-14</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>hack i död gran</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3403,41 +3374,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132497957</v>
+        <v>132499538</v>
       </c>
       <c r="B27" t="n">
-        <v>91918</v>
+        <v>57972</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3445,10 +3417,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>759681</v>
+        <v>760162</v>
       </c>
       <c r="R27" t="n">
-        <v>7177101</v>
+        <v>7177226</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3483,13 +3455,17 @@
           <t>2026-04-14</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>hack i död ved</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3508,41 +3484,42 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132499748</v>
+        <v>132499583</v>
       </c>
       <c r="B28" t="n">
-        <v>89300</v>
+        <v>57972</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>510</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3550,10 +3527,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>760175</v>
+        <v>760164</v>
       </c>
       <c r="R28" t="n">
-        <v>7177177</v>
+        <v>7177226</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3590,7 +3567,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>på toppbruten gran</t>
+          <t>hack i gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3599,7 +3576,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3618,27 +3594,27 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132498470</v>
+        <v>132499730</v>
       </c>
       <c r="B29" t="n">
-        <v>57958</v>
+        <v>57972</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3661,10 +3637,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>759751</v>
+        <v>760153</v>
       </c>
       <c r="R29" t="n">
-        <v>7177068</v>
+        <v>7177247</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3701,14 +3677,14 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>hack i rotben på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="b">
         <v>0</v>
@@ -3728,27 +3704,27 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132499673</v>
+        <v>132499893</v>
       </c>
       <c r="B30" t="n">
-        <v>57958</v>
+        <v>57972</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3771,10 +3747,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>760160</v>
+        <v>759943</v>
       </c>
       <c r="R30" t="n">
-        <v>7177228</v>
+        <v>7177168</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3811,14 +3787,14 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>barksprätt på två granar</t>
+          <t>hack i död ved</t>
         </is>
       </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="b">
         <v>0</v>
@@ -3838,42 +3814,42 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132497833</v>
+        <v>132497124</v>
       </c>
       <c r="B31" t="n">
-        <v>99130</v>
+        <v>57975</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3881,10 +3857,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>759652</v>
+        <v>759591</v>
       </c>
       <c r="R31" t="n">
-        <v>7177116</v>
+        <v>7177039</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3919,13 +3895,17 @@
           <t>2026-04-14</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF31" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3944,10 +3924,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132499026</v>
+        <v>132497438</v>
       </c>
       <c r="B32" t="n">
-        <v>79333</v>
+        <v>57975</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3955,30 +3935,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3986,10 +3967,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>760140</v>
+        <v>759602</v>
       </c>
       <c r="R32" t="n">
-        <v>7177159</v>
+        <v>7177096</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4024,13 +4005,17 @@
           <t>2026-04-14</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>barksprätt på två granar</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF32" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4049,10 +4034,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132499169</v>
+        <v>132497489</v>
       </c>
       <c r="B33" t="n">
-        <v>79333</v>
+        <v>57975</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4060,30 +4045,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4091,10 +4077,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>760150</v>
+        <v>759600</v>
       </c>
       <c r="R33" t="n">
-        <v>7177131</v>
+        <v>7177122</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4129,13 +4115,17 @@
           <t>2026-04-14</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF33" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4154,10 +4144,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132499730</v>
+        <v>132497587</v>
       </c>
       <c r="B34" t="n">
-        <v>57955</v>
+        <v>57975</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4165,16 +4155,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4197,10 +4187,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>760153</v>
+        <v>759611</v>
       </c>
       <c r="R34" t="n">
-        <v>7177247</v>
+        <v>7177137</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4237,14 +4227,14 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>hack i rotben på gran</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG34" t="b">
         <v>0</v>
@@ -4264,10 +4254,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132498603</v>
+        <v>132498057</v>
       </c>
       <c r="B35" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4307,10 +4297,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>759783</v>
+        <v>759701</v>
       </c>
       <c r="R35" t="n">
-        <v>7177071</v>
+        <v>7177107</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4374,10 +4364,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132497438</v>
+        <v>132498140</v>
       </c>
       <c r="B36" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4417,10 +4407,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>759602</v>
+        <v>759709</v>
       </c>
       <c r="R36" t="n">
-        <v>7177096</v>
+        <v>7177110</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4457,7 +4447,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>barksprätt på två granar</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4484,10 +4474,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132497587</v>
+        <v>132498370</v>
       </c>
       <c r="B37" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4527,10 +4517,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>759611</v>
+        <v>759732</v>
       </c>
       <c r="R37" t="n">
-        <v>7177137</v>
+        <v>7177063</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4567,14 +4557,14 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>färska ringhack på grov tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="b">
         <v>0</v>
@@ -4594,42 +4584,42 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132498962</v>
+        <v>132498451</v>
       </c>
       <c r="B38" t="n">
-        <v>99130</v>
+        <v>57975</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4637,10 +4627,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>760052</v>
+        <v>759745</v>
       </c>
       <c r="R38" t="n">
-        <v>7177092</v>
+        <v>7177069</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4675,13 +4665,17 @@
           <t>2026-04-14</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF38" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4700,10 +4694,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132499836</v>
+        <v>132498470</v>
       </c>
       <c r="B39" t="n">
-        <v>92217</v>
+        <v>57975</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4711,30 +4705,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4742,10 +4737,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>759978</v>
+        <v>759751</v>
       </c>
       <c r="R39" t="n">
-        <v>7177164</v>
+        <v>7177068</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4780,13 +4775,17 @@
           <t>2026-04-14</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4805,10 +4804,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132499538</v>
+        <v>132498603</v>
       </c>
       <c r="B40" t="n">
-        <v>57955</v>
+        <v>57975</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4816,16 +4815,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4848,10 +4847,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>760162</v>
+        <v>759783</v>
       </c>
       <c r="R40" t="n">
-        <v>7177226</v>
+        <v>7177071</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4888,14 +4887,14 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>hack i död ved</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG40" t="b">
         <v>0</v>
@@ -4915,10 +4914,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132498898</v>
+        <v>132498655</v>
       </c>
       <c r="B41" t="n">
-        <v>57955</v>
+        <v>57975</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4926,16 +4925,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4958,10 +4957,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>760051</v>
+        <v>759879</v>
       </c>
       <c r="R41" t="n">
-        <v>7177089</v>
+        <v>7177034</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4998,14 +4997,14 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>hack i död gran</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG41" t="b">
         <v>0</v>
@@ -5025,10 +5024,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132499504</v>
+        <v>132498725</v>
       </c>
       <c r="B42" t="n">
-        <v>57955</v>
+        <v>57975</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5036,16 +5035,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5068,10 +5067,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>760170</v>
+        <v>759984</v>
       </c>
       <c r="R42" t="n">
-        <v>7177214</v>
+        <v>7177051</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5108,14 +5107,14 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>hack i död gran</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG42" t="b">
         <v>0</v>
@@ -5135,10 +5134,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132499349</v>
+        <v>132498747</v>
       </c>
       <c r="B43" t="n">
-        <v>79333</v>
+        <v>57975</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5146,32 +5145,29 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -5181,10 +5177,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>760200</v>
+        <v>759997</v>
       </c>
       <c r="R43" t="n">
-        <v>7177185</v>
+        <v>7177045</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5221,16 +5217,15 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>fertil!</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF43" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5249,10 +5244,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132499017</v>
+        <v>132498803</v>
       </c>
       <c r="B44" t="n">
-        <v>79333</v>
+        <v>57975</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5260,30 +5255,31 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5291,10 +5287,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>760089</v>
+        <v>760014</v>
       </c>
       <c r="R44" t="n">
-        <v>7177139</v>
+        <v>7177057</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5329,13 +5325,17 @@
           <t>2026-04-14</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>gamla ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5354,10 +5354,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132498451</v>
+        <v>132498840</v>
       </c>
       <c r="B45" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5397,10 +5397,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>759745</v>
+        <v>760038</v>
       </c>
       <c r="R45" t="n">
-        <v>7177069</v>
+        <v>7177053</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5437,14 +5437,14 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="b">
         <v>0</v>
@@ -5464,42 +5464,42 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132498541</v>
+        <v>132498977</v>
       </c>
       <c r="B46" t="n">
-        <v>99130</v>
+        <v>57975</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5507,10 +5507,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>759757</v>
+        <v>760051</v>
       </c>
       <c r="R46" t="n">
-        <v>7177076</v>
+        <v>7177103</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5547,16 +5547,15 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>ca 1 x 0,3 m med bladrosetter</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF46" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5575,10 +5574,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132498655</v>
+        <v>132498999</v>
       </c>
       <c r="B47" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5618,10 +5617,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>759879</v>
+        <v>760075</v>
       </c>
       <c r="R47" t="n">
-        <v>7177034</v>
+        <v>7177098</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5682,6 +5681,984 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>132499331</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Råberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>760200</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7177185</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>132499673</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Råberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>760160</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7177228</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>barksprätt på två granar</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>132498686</v>
+      </c>
+      <c r="B50" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Råberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>759893</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7177023</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>typiska gnagspår på gran</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>132497833</v>
+      </c>
+      <c r="B51" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Råberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>759652</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7177116</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>132497859</v>
+      </c>
+      <c r="B52" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Råberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>759662</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7177107</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>132498541</v>
+      </c>
+      <c r="B53" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Råberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>759757</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7177076</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>ca 1 x 0,3 m med bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>132498962</v>
+      </c>
+      <c r="B54" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Råberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>760052</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7177092</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>132499258</v>
+      </c>
+      <c r="B55" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Råberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>760181</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7177119</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>ca 1 kvadratmeter med bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>132499287</v>
+      </c>
+      <c r="B56" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Råberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>760198</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7177126</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12578-2026 artfynd.xlsx
+++ b/artfynd/A 12578-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY56"/>
+  <dimension ref="A1:AZ56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132499748</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -887,6 +897,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132499836</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -992,6 +1007,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132497957</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1097,6 +1117,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132498407</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132498758</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1312,6 +1342,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132499783</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1422,6 +1457,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132499049</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1532,6 +1572,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132499759</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1637,6 +1682,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132497201</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132497762</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1847,6 +1902,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132498179</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1952,6 +2012,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132498224</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2057,6 +2122,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132499017</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2162,6 +2232,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132499026</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2267,6 +2342,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132499169</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2381,6 +2461,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132499349</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2491,6 +2576,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132499435</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2601,6 +2691,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132499553</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2711,6 +2806,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132496824</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2821,6 +2921,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132497934</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2931,6 +3036,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132498270</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3041,6 +3151,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132498323</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3151,6 +3266,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132498877</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3261,6 +3381,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132498898</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3371,6 +3496,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132499504</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3481,6 +3611,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132499538</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3591,6 +3726,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132499583</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3701,6 +3841,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132499730</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3811,6 +3956,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132499893</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3921,6 +4071,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132497124</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4031,6 +4186,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132497438</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4141,6 +4301,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132497489</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4251,6 +4416,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132497587</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4361,6 +4531,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132498057</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4471,6 +4646,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132498140</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4581,6 +4761,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132498370</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4691,6 +4876,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132498451</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4801,6 +4991,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132498470</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4911,6 +5106,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132498603</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5021,6 +5221,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132498655</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5131,6 +5336,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132498725</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5241,6 +5451,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132498747</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5351,6 +5566,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132498803</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5461,6 +5681,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132498840</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5571,6 +5796,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132498977</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5681,6 +5911,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132498999</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5791,6 +6026,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132499331</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5901,6 +6141,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132499673</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6013,6 +6258,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132498686</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6119,6 +6369,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132497833</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6225,6 +6480,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132497859</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6336,6 +6596,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132498541</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6442,6 +6707,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132498962</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6553,6 +6823,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132499258</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6659,8 +6934,70 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132499287</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>